--- a/results_fcgma/ResultsCompMethod.xlsx
+++ b/results_fcgma/ResultsCompMethod.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,8 +438,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[[1. 0. 0. ... 0. 0. 0.]
- [0. 0. 1. ... 0. 0. 0.]
+          <t>[[0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
  [0. 0. 0. ... 0. 0. 0.]
  ...
  [0. 0. 0. ... 0. 0. 0.]
@@ -448,11 +448,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>571.9532470703125</v>
+        <v>2.906599998474121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[547.602294921875, 552.4946899414062, 552.4946899414062, 552.4946899414062, 552.4946899414062, 554.5687866210938, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 570.8800659179688, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.838623046875, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125, 571.9532470703125]</t>
+          <t>[1.5867999792099, 1.5867999792099, 1.6944000720977783, 1.6944000720977783, 1.6944000720977783, 1.6944000720977783, 1.7349998950958252, 1.8868000507354736, 1.9223999977111816, 1.9223999977111816, 1.9223999977111816, 1.9223999977111816, 1.9316999912261963, 1.9986000061035156, 1.9986000061035156, 2.0384998321533203, 2.0384998321533203, 2.0384998321533203, 2.0441999435424805, 2.0441999435424805, 2.053799867630005, 2.053799867630005, 2.07889986038208, 2.07889986038208, 2.1768999099731445, 2.1768999099731445, 2.1768999099731445, 2.1768999099731445, 2.297799825668335, 2.3285000324249268, 2.3285000324249268, 2.3285000324249268, 2.3285000324249268, 2.33870005607605, 2.3486998081207275, 2.3486998081207275, 2.4594998359680176, 2.4594998359680176, 2.4594998359680176, 2.4594998359680176, 2.4594998359680176, 2.497799873352051, 2.497799873352051, 2.526399850845337, 2.526399850845337, 2.616799831390381, 2.616799831390381, 2.6282999515533447, 2.700200080871582, 2.700200080871582, 2.744500160217285, 2.7504000663757324, 2.7504000663757324, 2.779399871826172, 2.779399871826172, 2.779399871826172, 2.779399871826172, 2.787299871444702, 2.787299871444702, 2.800299882888794, 2.801100015640259, 2.801100015640259, 2.801100015640259, 2.805499792098999, 2.809199810028076, 2.8554999828338623, 2.8554999828338623, 2.8554999828338623, 2.864999771118164, 2.8706002235412598, 2.8706002235412598, 2.8706002235412598, 2.8706002235412598, 2.8706002235412598, 2.8706002235412598, 2.8706002235412598, 2.8706002235412598, 2.8706002235412598, 2.8706002235412598, 2.8706002235412598, 2.8706002235412598, 2.8810999393463135, 2.891900062561035, 2.891900062561035, 2.8934998512268066, 2.8934998512268066, 2.8934998512268066, 2.8934998512268066, 2.8934998512268066, 2.8934998512268066, 2.8934998512268066, 2.8934998512268066, 2.8934998512268066, 2.8994998931884766, 2.8994998931884766, 2.8994998931884766, 2.901099681854248, 2.901099681854248, 2.906599998474121, 2.906599998474121, 2.906599998474121]</t>
         </is>
       </c>
     </row>
@@ -464,21 +464,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[[1. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 1. ... 0. 0. 0.]
- ...
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]]</t>
+          <t>[[0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ ...
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 1.]]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>574.4638671875</v>
+        <v>2.485899925231934</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[547.602294921875, 547.602294921875, 548.5890502929688, 554.3598022460938, 554.8607177734375, 554.8607177734375, 554.8607177734375, 554.8607177734375, 554.8607177734375, 557.3465576171875, 557.3465576171875, 560.3350830078125, 560.3350830078125, 563.3157348632812, 563.3157348632812, 563.3157348632812, 563.3157348632812, 563.3157348632812, 563.3157348632812, 563.3157348632812, 563.3157348632812, 563.3157348632812, 563.3157348632812, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 568.5697021484375, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 570.4391479492188, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875, 574.4638671875]</t>
+          <t>[1.5867999792099, 1.722599983215332, 1.722599983215332, 1.722599983215332, 1.722599983215332, 1.722599983215332, 1.821699857711792, 1.821699857711792, 1.9066998958587646, 1.9066998958587646, 1.9066998958587646, 2.0226998329162598, 2.063499927520752, 2.1387999057769775, 2.1387999057769775, 2.1387999057769775, 2.156099796295166, 2.156099796295166, 2.156099796295166, 2.1861000061035156, 2.1861000061035156, 2.1861000061035156, 2.196199893951416, 2.273099899291992, 2.273099899291992, 2.273099899291992, 2.273099899291992, 2.273099899291992, 2.3076000213623047, 2.3076000213623047, 2.3353002071380615, 2.3353002071380615, 2.3353002071380615, 2.3353002071380615, 2.3696999549865723, 2.3696999549865723, 2.3696999549865723, 2.3696999549865723, 2.3696999549865723, 2.3889000415802, 2.4135000705718994, 2.419100046157837, 2.419100046157837, 2.419100046157837, 2.419100046157837, 2.419100046157837, 2.419100046157837, 2.419100046157837, 2.4355998039245605, 2.4355998039245605, 2.4355998039245605, 2.4355998039245605, 2.4535000324249268, 2.4535000324249268, 2.472899913787842, 2.472899913787842, 2.472899913787842, 2.472899913787842, 2.4784998893737793, 2.4784998893737793, 2.4784998893737793, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336, 2.4858999252319336]</t>
         </is>
       </c>
     </row>
@@ -490,21 +490,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[[1. 0. 0. ... 0. 0. 0.]
- [0. 0. 1. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- ...
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]]</t>
+          <t>[[0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ ...
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 1. 0.]]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>576.7672119140625</v>
+        <v>2.319900035858154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[547.602294921875, 547.602294921875, 553.8333129882812, 554.8280029296875, 554.8280029296875, 554.8280029296875, 554.8280029296875, 554.8280029296875, 559.8421630859375, 559.8421630859375, 559.8421630859375, 559.8421630859375, 559.851806640625, 559.851806640625, 559.851806640625, 559.851806640625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625, 576.7672119140625]</t>
+          <t>[1.5867999792099, 1.5867999792099, 1.5867999792099, 1.5867999792099, 1.6238999366760254, 1.867999792098999, 1.867999792098999, 1.867999792098999, 1.867999792098999, 1.867999792098999, 1.867999792098999, 1.867999792098999, 1.867999792098999, 1.867999792098999, 1.9306998252868652, 1.9306998252868652, 1.9306998252868652, 1.9306998252868652, 1.9306998252868652, 1.9306998252868652, 1.9306998252868652, 1.9306998252868652, 1.9306998252868652, 1.9306998252868652, 1.9529001712799072, 1.9529001712799072, 1.9529001712799072, 1.9592998027801514, 2.024399757385254, 2.024399757385254, 2.024399757385254, 2.024399757385254, 2.027400016784668, 2.053100109100342, 2.053100109100342, 2.1187000274658203, 2.123499870300293, 2.123499870300293, 2.1422998905181885, 2.1422998905181885, 2.1775999069213867, 2.1828999519348145, 2.1828999519348145, 2.1828999519348145, 2.1828999519348145, 2.1828999519348145, 2.1828999519348145, 2.1828999519348145, 2.190999984741211, 2.22379994392395, 2.22379994392395, 2.2596001625061035, 2.2596001625061035, 2.2596001625061035, 2.2691001892089844, 2.269400119781494, 2.269400119781494, 2.274700164794922, 2.297600030899048, 2.297600030899048, 2.297600030899048, 2.297600030899048, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3070998191833496, 2.3078999519348145, 2.3078999519348145, 2.3078999519348145, 2.3078999519348145, 2.3078999519348145, 2.3078999519348145, 2.3078999519348145, 2.3190999031066895, 2.3199000358581543, 2.3199000358581543, 2.3199000358581543, 2.3199000358581543, 2.3199000358581543, 2.3199000358581543, 2.3199000358581543, 2.3199000358581543]</t>
         </is>
       </c>
     </row>
@@ -516,21 +516,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[[0. 1. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- ...
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]]</t>
+          <t>[[0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ ...
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 1.]]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>574.0414428710938</v>
+        <v>2.833199977874756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[547.602294921875, 547.602294921875, 547.602294921875, 547.602294921875, 551.9946899414062, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 560.4426879882812, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 562.060791015625, 564.5723266601562, 564.5723266601562, 564.5723266601562, 564.5723266601562, 564.5723266601562, 564.5723266601562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 565.3174438476562, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938, 574.0414428710938]</t>
+          <t>[1.5867999792099, 1.5867999792099, 1.5867999792099, 1.5867999792099, 1.5867999792099, 1.7991998195648193, 1.80430006980896, 1.80430006980896, 1.80430006980896, 1.8315000534057617, 1.8715999126434326, 1.8715999126434326, 1.904599905014038, 1.904599905014038, 1.904599905014038, 1.904599905014038, 1.904599905014038, 1.904599905014038, 1.904599905014038, 1.9089000225067139, 1.9590997695922852, 2.0032999515533447, 2.0032999515533447, 2.0032999515533447, 2.00600004196167, 2.166599988937378, 2.166599988937378, 2.166599988937378, 2.166599988937378, 2.166599988937378, 2.166599988937378, 2.194999933242798, 2.194999933242798, 2.194999933242798, 2.194999933242798, 2.200500011444092, 2.200500011444092, 2.210899829864502, 2.210899829864502, 2.243799924850464, 2.243799924850464, 2.243799924850464, 2.26200008392334, 2.2709999084472656, 2.3355000019073486, 2.3355000019073486, 2.3355000019073486, 2.3355000019073486, 2.4302000999450684, 2.444700002670288, 2.444700002670288, 2.444700002670288, 2.444700002670288, 2.5083999633789062, 2.511199951171875, 2.5139000415802, 2.5139000415802, 2.5378000736236572, 2.5378000736236572, 2.5388998985290527, 2.5388998985290527, 2.654399871826172, 2.654399871826172, 2.654399871826172, 2.654399871826172, 2.6654000282287598, 2.6654000282287598, 2.674799919128418, 2.693000078201294, 2.7216997146606445, 2.7216997146606445, 2.7216997146606445, 2.757499933242798, 2.757499933242798, 2.757499933242798, 2.7612998485565186, 2.7612998485565186, 2.777100086212158, 2.7811999320983887, 2.795599937438965, 2.795599937438965, 2.7973999977111816, 2.7973999977111816, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.8011999130249023, 2.829400062561035, 2.829400062561035, 2.829400062561035, 2.833199977874756, 2.833199977874756]</t>
         </is>
       </c>
     </row>
@@ -542,21 +542,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[[1. 0. 0. ... 0. 0. 0.]
- [0. 0. 1. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- ...
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]]</t>
+          <t>[[0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ ...
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 1.]]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>579.9100341796875</v>
+        <v>3.031800031661987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[547.602294921875, 547.602294921875, 547.7874755859375, 551.4197998046875, 551.9417724609375, 551.9417724609375, 551.9417724609375, 558.9391479492188, 558.9391479492188, 558.9391479492188, 558.9391479492188, 560.42333984375, 560.42333984375, 560.42333984375, 560.42333984375, 560.42333984375, 560.42333984375, 560.42333984375, 560.42333984375, 560.42333984375, 560.42333984375, 560.42333984375, 561.5220947265625, 561.5220947265625, 561.5220947265625, 561.5220947265625, 561.5220947265625, 561.5687866210938, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 573.7760009765625, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875, 579.9100341796875]</t>
+          <t>[1.5867999792099, 1.5867999792099, 1.6644001007080078, 1.6644001007080078, 1.7740001678466797, 1.7740001678466797, 1.7740001678466797, 1.9724000692367554, 1.9724000692367554, 1.9724000692367554, 2.1308000087738037, 2.1308000087738037, 2.1308000087738037, 2.1308000087738037, 2.1308000087738037, 2.1308000087738037, 2.1851000785827637, 2.1851000785827637, 2.1851000785827637, 2.1851000785827637, 2.1851000785827637, 2.1851000785827637, 2.1851000785827637, 2.1851000785827637, 2.2313997745513916, 2.2699999809265137, 2.2699999809265137, 2.2923998832702637, 2.297299861907959, 2.359099864959717, 2.359099864959717, 2.359099864959717, 2.359099864959717, 2.44920015335083, 2.44920015335083, 2.4843997955322266, 2.4843997955322266, 2.4843997955322266, 2.5308997631073, 2.5350000858306885, 2.682499885559082, 2.785600185394287, 2.785600185394287, 2.785600185394287, 2.785600185394287, 2.785600185394287, 2.7992000579833984, 2.803299903869629, 2.80649995803833, 2.8147997856140137, 2.82919979095459, 2.82919979095459, 2.8310999870300293, 2.8310999870300293, 2.831699848175049, 2.862100124359131, 2.8894999027252197, 2.8894999027252197, 2.8894999027252197, 2.8944997787475586, 2.8944997787475586, 2.8944997787475586, 2.900099754333496, 2.9025001525878906, 2.9028000831604004, 2.9028000831604004, 2.92110013961792, 2.92110013961792, 2.9226999282836914, 2.9226999282836914, 2.9226999282836914, 2.9930999279022217, 2.995300054550171, 2.995300054550171, 2.997999906539917, 2.997999906539917, 3.00219988822937, 3.002500057220459, 3.002500057220459, 3.026599884033203, 3.0293002128601074, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0315001010894775, 3.0318000316619873, 3.0318000316619873, 3.0318000316619873, 3.0318000316619873]</t>
         </is>
       </c>
     </row>
@@ -568,21 +568,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[1. 0. 0. ... 0. 0. 0.]
- [0. 1. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- ...
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]]</t>
+          <t>[[0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ ...
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 1.]]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>578.6516723632812</v>
+        <v>2.765899896621704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[547.602294921875, 547.602294921875, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.4744262695312, 559.7645263671875, 559.7645263671875, 559.7645263671875, 559.7645263671875, 559.7645263671875, 559.7645263671875, 559.7645263671875, 559.7645263671875, 559.7645263671875, 559.7645263671875, 559.7645263671875, 559.7645263671875, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812, 578.6516723632812]</t>
+          <t>[1.5867999792099, 1.6921000480651855, 1.6921000480651855, 1.6921000480651855, 1.6921000480651855, 1.6921000480651855, 1.6921000480651855, 1.9453999996185303, 1.9453999996185303, 1.9453999996185303, 1.9453999996185303, 2.1001999378204346, 2.213099956512451, 2.213099956512451, 2.238100051879883, 2.238100051879883, 2.2555999755859375, 2.2555999755859375, 2.2555999755859375, 2.2555999755859375, 2.257200002670288, 2.3094000816345215, 2.3094000816345215, 2.3273000717163086, 2.3273000717163086, 2.3273000717163086, 2.3273000717163086, 2.3273000717163086, 2.3273000717163086, 2.3903000354766846, 2.3951001167297363, 2.3951001167297363, 2.4524998664855957, 2.4788999557495117, 2.541100025177002, 2.541100025177002, 2.541100025177002, 2.541100025177002, 2.541100025177002, 2.541100025177002, 2.541100025177002, 2.541100025177002, 2.5911002159118652, 2.5911002159118652, 2.5911002159118652, 2.5911002159118652, 2.594299793243408, 2.6131999492645264, 2.6159000396728516, 2.6232001781463623, 2.627000093460083, 2.627000093460083, 2.6311001777648926, 2.6311001777648926, 2.6793999671936035, 2.6793999671936035, 2.6793999671936035, 2.682999849319458, 2.710400104522705, 2.710400104522705, 2.7140002250671387, 2.7140002250671387, 2.722899913787842, 2.722899913787842, 2.722899913787842, 2.7265000343322754, 2.7296998500823975, 2.7331998348236084, 2.7466001510620117, 2.7519001960754395, 2.7519001960754395, 2.753199815750122, 2.753199815750122, 2.753199815750122, 2.7604000568389893, 2.7604000568389893, 2.7604000568389893, 2.7647998332977295, 2.7647998332977295, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704, 2.765899896621704]</t>
         </is>
       </c>
     </row>
@@ -594,21 +594,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[[1. 0. 0. ... 0. 0. 0.]
- [0. 1. 0. ... 0. 0. 0.]
- [0. 0. 1. ... 0. 0. 0.]
- ...
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]]</t>
+          <t>[[0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ ...
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 1.]]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>570.275146484375</v>
+        <v>2.584800004959106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[547.602294921875, 547.602294921875, 547.602294921875, 550.811279296875, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 562.9365234375, 565.5970458984375, 565.5970458984375, 565.5970458984375, 565.5970458984375, 565.5970458984375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375, 570.275146484375]</t>
+          <t>[1.5867999792099, 1.5867999792099, 1.5867999792099, 1.5867999792099, 1.5867999792099, 1.615799903869629, 1.7701001167297363, 1.8823997974395752, 1.8823997974395752, 1.9112000465393066, 1.9112000465393066, 1.9617998600006104, 1.9617998600006104, 1.9617998600006104, 2.119499921798706, 2.148699998855591, 2.148699998855591, 2.170599937438965, 2.170599937438965, 2.170599937438965, 2.170599937438965, 2.170599937438965, 2.170599937438965, 2.170599937438965, 2.2091000080108643, 2.2091000080108643, 2.2091000080108643, 2.2091000080108643, 2.210899829864502, 2.219899892807007, 2.219899892807007, 2.2788000106811523, 2.2821998596191406, 2.2821998596191406, 2.3087000846862793, 2.3087000846862793, 2.3087000846862793, 2.3087000846862793, 2.3087000846862793, 2.3087000846862793, 2.3087000846862793, 2.3203999996185303, 2.3222999572753906, 2.3222999572753906, 2.3262999057769775, 2.380699872970581, 2.40939998626709, 2.417099952697754, 2.468400001525879, 2.468400001525879, 2.468400001525879, 2.468400001525879, 2.468400001525879, 2.4779999256134033, 2.4919002056121826, 2.4919002056121826, 2.5201001167297363, 2.5201001167297363, 2.5201001167297363, 2.5201001167297363, 2.521699905395508, 2.521699905395508, 2.521699905395508, 2.521699905395508, 2.523200035095215, 2.5274996757507324, 2.5274996757507324, 2.529099941253662, 2.529099941253662, 2.529099941253662, 2.5443999767303467, 2.5460000038146973, 2.550999879837036, 2.567699909210205, 2.567699909210205, 2.567699909210205, 2.5795998573303223, 2.5795998573303223, 2.5795998573303223, 2.5795998573303223, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064, 2.5848000049591064]</t>
         </is>
       </c>
     </row>
@@ -620,8 +620,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[[1. 0. 0. ... 0. 0. 0.]
- [0. 1. 0. ... 0. 0. 0.]
+          <t>[[0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
  [0. 0. 0. ... 0. 0. 0.]
  ...
  [0. 0. 0. ... 0. 0. 0.]
@@ -630,11 +630,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>583.7380981445312</v>
+        <v>2.675100088119507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[547.602294921875, 556.0873413085938, 556.0873413085938, 565.8218994140625, 565.8218994140625, 565.8218994140625, 565.8218994140625, 565.8218994140625, 565.8218994140625, 565.8218994140625, 565.8218994140625, 565.8218994140625, 565.8218994140625, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 566.447998046875, 569.034423828125, 569.034423828125, 569.034423828125, 569.034423828125, 569.034423828125, 569.034423828125, 569.034423828125, 569.034423828125, 569.034423828125, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 571.2980346679688, 572.2998046875, 572.2998046875, 572.2998046875, 572.2998046875, 572.2998046875, 572.2998046875, 572.2998046875, 572.2998046875, 572.2998046875, 572.2998046875, 572.2998046875, 576.736328125, 576.736328125, 576.736328125, 576.736328125, 576.736328125, 576.736328125, 576.736328125, 576.736328125, 576.736328125, 579.7389526367188, 579.7389526367188, 579.7389526367188, 579.7389526367188, 580.239013671875, 580.239013671875, 580.239013671875, 582.738037109375, 582.738037109375, 582.738037109375, 582.738037109375, 582.738037109375, 583.238037109375, 583.238037109375, 583.238037109375, 583.2380981445312, 583.7380981445312, 583.7380981445312]</t>
+          <t>[1.5867999792099, 1.5867999792099, 1.5867999792099, 1.5867999792099, 1.5867999792099, 1.8042998313903809, 1.8042998313903809, 1.8187999725341797, 1.8187999725341797, 1.8820998668670654, 1.8820998668670654, 1.915099859237671, 1.9398000240325928, 1.9398000240325928, 1.9398000240325928, 1.9398000240325928, 1.9728000164031982, 1.9728000164031982, 1.9728000164031982, 1.9728000164031982, 2.028599977493286, 2.1391000747680664, 2.1391000747680664, 2.1391000747680664, 2.1391000747680664, 2.1391000747680664, 2.3542001247406006, 2.3542001247406006, 2.3542001247406006, 2.3542001247406006, 2.3542001247406006, 2.3542001247406006, 2.3542001247406006, 2.3542001247406006, 2.3542001247406006, 2.3635001182556152, 2.3635001182556152, 2.3635001182556152, 2.3635001182556152, 2.3933000564575195, 2.442700147628784, 2.442700147628784, 2.444700002670288, 2.4672000408172607, 2.4672000408172607, 2.527899980545044, 2.527899980545044, 2.527899980545044, 2.527899980545044, 2.580900192260742, 2.580900192260742, 2.589400053024292, 2.589400053024292, 2.589400053024292, 2.5992002487182617, 2.5992002487182617, 2.603400230407715, 2.621799945831299, 2.640500068664551, 2.640500068664551, 2.646199941635132, 2.646399974822998, 2.665099859237671, 2.665099859237671, 2.6748998165130615, 2.6748998165130615, 2.6748998165130615, 2.6748998165130615, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507, 2.675100088119507]</t>
         </is>
       </c>
     </row>
@@ -646,21 +646,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[[0. 1. 0. ... 0. 0. 0.]
- [0. 0. 1. ... 0. 0. 0.]
- [1. 0. 0. ... 0. 0. 0.]
- ...
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]]</t>
+          <t>[[0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ ...
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 1.]]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>579.3695068359375</v>
+        <v>3.239000082015991</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[547.602294921875, 547.602294921875, 550.52294921875, 550.7716064453125, 551.6693115234375, 552.6834106445312, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 563.397705078125, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375, 579.3695068359375]</t>
+          <t>[1.5867999792099, 1.5867999792099, 1.5867999792099, 1.7130999565124512, 1.7130999565124512, 1.7130999565124512, 1.7130999565124512, 1.8083999156951904, 1.8987998962402344, 1.8987998962402344, 1.8987998962402344, 1.8987998962402344, 1.8987998962402344, 1.8987998962402344, 1.8987998962402344, 1.9667999744415283, 1.9960999488830566, 1.9960999488830566, 1.9960999488830566, 1.9960999488830566, 2.005199909210205, 2.005199909210205, 2.2242000102996826, 2.2242000102996826, 2.2242000102996826, 2.2242000102996826, 2.452699899673462, 2.452699899673462, 2.452699899673462, 2.452699899673462, 2.580700159072876, 2.580700159072876, 2.580700159072876, 2.5904998779296875, 2.5904998779296875, 2.725299835205078, 2.725299835205078, 2.725299835205078, 2.7934000492095947, 2.7934000492095947, 2.906400203704834, 2.906400203704834, 2.9149999618530273, 2.9149999618530273, 2.9149999618530273, 2.9149999618530273, 2.925600051879883, 2.925600051879883, 2.925600051879883, 3.002500057220459, 3.005200147628784, 3.021899700164795, 3.021899700164795, 3.0362000465393066, 3.0362000465393066, 3.0495998859405518, 3.0554001331329346, 3.0618999004364014, 3.072999954223633, 3.082900047302246, 3.082900047302246, 3.1718997955322266, 3.1718997955322266, 3.1718997955322266, 3.1718997955322266, 3.1718997955322266, 3.1813998222351074, 3.190999984741211, 3.190999984741211, 3.190999984741211, 3.200500011444092, 3.200500011444092, 3.200500011444092, 3.200500011444092, 3.2076001167297363, 3.2076001167297363, 3.2119998931884766, 3.2119998931884766, 3.219099998474121, 3.219099998474121, 3.219099998474121, 3.219099998474121, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991, 3.239000082015991]</t>
         </is>
       </c>
     </row>
@@ -672,21 +672,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[[1. 0. 0. ... 0. 0. 0.]
- [0. 1. 0. ... 0. 0. 0.]
- [0. 0. 1. ... 0. 0. 0.]
- ...
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]
- [0. 0. 0. ... 0. 0. 0.]]</t>
+          <t>[[0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ ...
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 0.]
+ [0. 0. 0. ... 0. 0. 1.]]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>570.43212890625</v>
+        <v>3.125799894332886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[547.602294921875, 547.602294921875, 552.0379028320312, 552.0379028320312, 552.0379028320312, 552.0379028320312, 553.4664916992188, 553.4664916992188, 562.41357421875, 562.41357421875, 562.41357421875, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 564.9805908203125, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625, 570.43212890625]</t>
+          <t>[1.5867999792099, 1.5867999792099, 1.5867999792099, 1.6017000675201416, 1.6017000675201416, 1.8355998992919922, 1.8355998992919922, 1.8355998992919922, 1.8355998992919922, 1.8355998992919922, 2.037100076675415, 2.037100076675415, 2.037100076675415, 2.037100076675415, 2.037100076675415, 2.1236000061035156, 2.1236000061035156, 2.1236000061035156, 2.1236000061035156, 2.149199962615967, 2.149199962615967, 2.1577999591827393, 2.197700023651123, 2.197700023651123, 2.197700023651123, 2.197700023651123, 2.381199836730957, 2.381199836730957, 2.3899998664855957, 2.573199987411499, 2.573199987411499, 2.589899778366089, 2.589899778366089, 2.5904998779296875, 2.628699779510498, 2.628699779510498, 2.628699779510498, 2.628699779510498, 2.6977999210357666, 2.6977999210357666, 2.700199842453003, 2.700199842453003, 2.724400043487549, 2.724400043487549, 2.7269999980926514, 2.7348999977111816, 2.7348999977111816, 2.7348999977111816, 2.774099826812744, 2.774099826812744, 2.774099826812744, 2.788400173187256, 2.788400173187256, 2.830599784851074, 2.830599784851074, 2.830599784851074, 2.839600086212158, 2.839600086212158, 2.8425002098083496, 2.8425002098083496, 2.8428001403808594, 2.8800997734069824, 2.881999969482422, 2.881999969482422, 2.908100128173828, 2.908100128173828, 2.9175000190734863, 2.9175000190734863, 2.9351999759674072, 2.949699878692627, 2.949699878692627, 2.949699878692627, 2.949699878692627, 2.9643001556396484, 2.9695000648498535, 2.9695000648498535, 3.018899917602539, 3.0223000049591064, 3.0416998863220215, 3.0416998863220215, 3.0416998863220215, 3.0556998252868652, 3.0909998416900635, 3.096099853515625, 3.1057000160217285, 3.11329984664917, 3.11329984664917, 3.11329984664917, 3.1181998252868652, 3.1181998252868652, 3.1181998252868652, 3.1257998943328857, 3.1257998943328857, 3.1257998943328857, 3.1257998943328857, 3.1257998943328857, 3.1257998943328857, 3.1257998943328857, 3.1257998943328857, 3.1257998943328857, 3.1257998943328857]</t>
         </is>
       </c>
     </row>
